--- a/samples/official-attendance/official-attendance_sheet_sample.xlsx
+++ b/samples/official-attendance/official-attendance_sheet_sample.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>샘플가온</t>
+          <t>서주원</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>샘플나래</t>
+          <t>박민재</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>샘플다솜</t>
+          <t>이하은</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>샘플라온</t>
+          <t>정도윤</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>샘플마루</t>
+          <t>최지우</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>샘플바다</t>
+          <t>강예준</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>샘플없는사람</t>
+          <t>윤태민</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>샘플없는사람: 과정에 등록되지 않은 사람(오류 행 시험).</t>
+          <t>윤태민: 과정에 등록되지 않은 사람(오류 행 시험).</t>
         </is>
       </c>
     </row>
